--- a/data/trans_bre/P1416-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1416-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>3,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,09</t>
+          <t>0,87; 5,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,71</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,58</t>
+          <t>-1,12; 3,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,22</t>
+          <t>-0,23; 6,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 148,61</t>
+          <t>12,48; 148,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 146,73</t>
+          <t>-1,92; 157,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 108,91</t>
+          <t>-22,11; 116,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 83,76</t>
+          <t>-2,2; 87,93</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,93</t>
+          <t>-0,28; 4,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,3</t>
+          <t>-0,1; 4,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,12</t>
+          <t>2,66; 6,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 7,04</t>
+          <t>-1,81; 3,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 80,46</t>
+          <t>-3,53; 81,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 90,58</t>
+          <t>-1,63; 93,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,08; 205,85</t>
+          <t>44,4; 193,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 163,44</t>
+          <t>-15,38; 47,02</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-23,4%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,51</t>
+          <t>-0,05; 5,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,56</t>
+          <t>-1,31; 3,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,01</t>
+          <t>1,88; 6,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 1,56</t>
+          <t>-1,94; 4,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 118,58</t>
+          <t>-1,54; 121,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 83,52</t>
+          <t>-19,99; 87,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,71; 283,3</t>
+          <t>40,01; 269,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 13,63</t>
+          <t>-13,93; 47,42</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>3,49</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,83</t>
+          <t>0,42; 5,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,27</t>
+          <t>0,82; 5,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,43</t>
+          <t>-1,43; 3,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,28</t>
+          <t>0,55; 6,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 91,14</t>
+          <t>4,0; 91,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 131,38</t>
+          <t>10,18; 128,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 61,29</t>
+          <t>-17,79; 59,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 69,69</t>
+          <t>6,23; 83,82</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,21</t>
+          <t>1,51; 4,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,39</t>
+          <t>1,08; 3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,21</t>
+          <t>1,78; 4,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,48</t>
+          <t>0,81; 3,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,84; 69,12</t>
+          <t>21,13; 68,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 72,17</t>
+          <t>18,22; 74,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,34; 94,45</t>
+          <t>31,45; 93,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 43,74</t>
+          <t>7,61; 42,38</t>
         </is>
       </c>
     </row>
